--- a/data/nzd0565/nzd0565.xlsx
+++ b/data/nzd0565/nzd0565.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E953"/>
+  <dimension ref="A1:E955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20443,6 +20443,48 @@
         <v>201.13</v>
       </c>
       <c r="E953" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B954" t="n">
+        <v>215.53</v>
+      </c>
+      <c r="C954" t="n">
+        <v>209.94</v>
+      </c>
+      <c r="D954" t="n">
+        <v>200.51</v>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B955" t="n">
+        <v>216.14</v>
+      </c>
+      <c r="C955" t="n">
+        <v>210.77</v>
+      </c>
+      <c r="D955" t="n">
+        <v>200.43</v>
+      </c>
+      <c r="E955" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20459,7 +20501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1086"/>
+  <dimension ref="A1:B1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31322,6 +31364,26 @@
       </c>
       <c r="B1086" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1087" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1088" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -31484,28 +31546,28 @@
         <v>0.1302</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03099337466978892</v>
+        <v>-0.03059339517392949</v>
       </c>
       <c r="J2" t="n">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="K2" t="n">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006680924623007845</v>
+        <v>0.006540502918630176</v>
       </c>
       <c r="M2" t="n">
-        <v>2.433566396803538</v>
+        <v>2.430557325054415</v>
       </c>
       <c r="N2" t="n">
-        <v>8.350179958360179</v>
+        <v>8.334778967581604</v>
       </c>
       <c r="O2" t="n">
-        <v>2.889667793771488</v>
+        <v>2.887001726286565</v>
       </c>
       <c r="P2" t="n">
-        <v>215.7108954318181</v>
+        <v>215.706739552979</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31556,28 +31618,28 @@
         <v>0.0954</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05159995780979643</v>
+        <v>-0.05112043537421945</v>
       </c>
       <c r="J3" t="n">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="K3" t="n">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01953614505854551</v>
+        <v>0.01926539636994451</v>
       </c>
       <c r="M3" t="n">
-        <v>2.272464632406413</v>
+        <v>2.270247577187456</v>
       </c>
       <c r="N3" t="n">
-        <v>7.837725065405587</v>
+        <v>7.824433899744113</v>
       </c>
       <c r="O3" t="n">
-        <v>2.799593732205726</v>
+        <v>2.797218958133973</v>
       </c>
       <c r="P3" t="n">
-        <v>210.5944484624766</v>
+        <v>210.5894780648893</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31628,28 +31690,28 @@
         <v>0.1109</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07164437978750099</v>
+        <v>-0.07200408351200149</v>
       </c>
       <c r="J4" t="n">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="K4" t="n">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04444705323755738</v>
+        <v>0.04507195265289277</v>
       </c>
       <c r="M4" t="n">
-        <v>2.009531207706412</v>
+        <v>2.007116990234836</v>
       </c>
       <c r="N4" t="n">
-        <v>6.472538659158891</v>
+        <v>6.460539969573077</v>
       </c>
       <c r="O4" t="n">
-        <v>2.544118444404444</v>
+        <v>2.541759227301649</v>
       </c>
       <c r="P4" t="n">
-        <v>203.2771626669214</v>
+        <v>203.2808899696422</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31687,7 +31749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E953"/>
+  <dimension ref="A1:E955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57417,6 +57479,60 @@
         </is>
       </c>
     </row>
+    <row r="954">
+      <c r="A954" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>-41.0194455965853,173.0184266123098</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>-41.018746426696886,173.01846904140194</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>-41.01808239165683,173.01875741656602</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>-41.0194457771277,173.01843386366312</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>-41.01874796202927,173.0184787028493</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>-41.01808191489307,173.01875670305714</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0565/nzd0565.xlsx
+++ b/data/nzd0565/nzd0565.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E955"/>
+  <dimension ref="A1:E959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20485,6 +20485,90 @@
         <v>200.43</v>
       </c>
       <c r="E955" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B956" t="n">
+        <v>216.59</v>
+      </c>
+      <c r="C956" t="n">
+        <v>210.74</v>
+      </c>
+      <c r="D956" t="n">
+        <v>200.64</v>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B957" t="n">
+        <v>216.4</v>
+      </c>
+      <c r="C957" t="n">
+        <v>211.15</v>
+      </c>
+      <c r="D957" t="n">
+        <v>200.42</v>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:12+00:00</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>216.19</v>
+      </c>
+      <c r="C958" t="n">
+        <v>210.99</v>
+      </c>
+      <c r="D958" t="n">
+        <v>200.04</v>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>216.39</v>
+      </c>
+      <c r="C959" t="n">
+        <v>211.17</v>
+      </c>
+      <c r="D959" t="n">
+        <v>200.26</v>
+      </c>
+      <c r="E959" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20501,7 +20585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1088"/>
+  <dimension ref="A1:B1092"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31384,6 +31468,46 @@
       </c>
       <c r="B1088" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1089" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1091" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1092" t="n">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>
@@ -31546,28 +31670,28 @@
         <v>0.1302</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03059339517392949</v>
+        <v>-0.0293436002822185</v>
       </c>
       <c r="J2" t="n">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="K2" t="n">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006540502918630176</v>
+        <v>0.00607148955921577</v>
       </c>
       <c r="M2" t="n">
-        <v>2.430557325054415</v>
+        <v>2.426892594495327</v>
       </c>
       <c r="N2" t="n">
-        <v>8.334778967581604</v>
+        <v>8.309485501472373</v>
       </c>
       <c r="O2" t="n">
-        <v>2.887001726286565</v>
+        <v>2.882617820917711</v>
       </c>
       <c r="P2" t="n">
-        <v>215.706739552979</v>
+        <v>215.6937202773805</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31618,28 +31742,28 @@
         <v>0.0954</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05112043537421945</v>
+        <v>-0.0496331393049659</v>
       </c>
       <c r="J3" t="n">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="K3" t="n">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01926539636994451</v>
+        <v>0.01832288163142359</v>
       </c>
       <c r="M3" t="n">
-        <v>2.270247577187456</v>
+        <v>2.268591927600975</v>
       </c>
       <c r="N3" t="n">
-        <v>7.824433899744113</v>
+        <v>7.805345242557572</v>
       </c>
       <c r="O3" t="n">
-        <v>2.797218958133973</v>
+        <v>2.793804796788346</v>
       </c>
       <c r="P3" t="n">
-        <v>210.5894780648893</v>
+        <v>210.5740204953906</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31690,28 +31814,28 @@
         <v>0.1109</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07200408351200149</v>
+        <v>-0.07281831054300403</v>
       </c>
       <c r="J4" t="n">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="K4" t="n">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04507195265289277</v>
+        <v>0.04644751672124081</v>
       </c>
       <c r="M4" t="n">
-        <v>2.007116990234836</v>
+        <v>2.002786053282105</v>
       </c>
       <c r="N4" t="n">
-        <v>6.460539969573077</v>
+        <v>6.437793374547754</v>
       </c>
       <c r="O4" t="n">
-        <v>2.541759227301649</v>
+        <v>2.537280704720657</v>
       </c>
       <c r="P4" t="n">
-        <v>203.2808899696422</v>
+        <v>203.2893534046953</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31749,7 +31873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E955"/>
+  <dimension ref="A1:E959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57533,6 +57657,114 @@
         </is>
       </c>
     </row>
+    <row r="956">
+      <c r="A956" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>-41.019445910314396,173.01843921302216</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>-41.01874790653534,173.01847835364038</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>-41.018083166397915,173.01875857601803</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>-41.01944585408005,173.0184369544039</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>-41.01874866495228,173.01848312616275</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>-41.018081855297595,173.01875661386853</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:12+00:00</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>-41.01944579192622,173.01843445803635</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>-41.01874836898472,173.018481263715</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>-41.01807959066972,173.0187532247014</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>-41.01944585112033,173.01843683552926</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>-41.018748701948205,173.0184833589687</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>-41.01808090177009,173.01875518685077</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0565/nzd0565.xlsx
+++ b/data/nzd0565/nzd0565.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E959"/>
+  <dimension ref="A1:E962"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20569,6 +20569,69 @@
         <v>200.26</v>
       </c>
       <c r="E959" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:16+00:00</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>216.98</v>
+      </c>
+      <c r="C960" t="n">
+        <v>210.57</v>
+      </c>
+      <c r="D960" t="n">
+        <v>199.07</v>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>216.94</v>
+      </c>
+      <c r="C961" t="n">
+        <v>210.54</v>
+      </c>
+      <c r="D961" t="n">
+        <v>199.35</v>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>216.51</v>
+      </c>
+      <c r="C962" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="D962" t="n">
+        <v>199.05</v>
+      </c>
+      <c r="E962" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20585,7 +20648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1092"/>
+  <dimension ref="A1:B1095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31508,6 +31571,36 @@
       </c>
       <c r="B1092" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1093" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1094" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1095" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -31670,28 +31763,28 @@
         <v>0.1302</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0293436002822185</v>
+        <v>-0.02816141294035362</v>
       </c>
       <c r="J2" t="n">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="K2" t="n">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00607148955921577</v>
+        <v>0.005627585090879905</v>
       </c>
       <c r="M2" t="n">
-        <v>2.426892594495327</v>
+        <v>2.425387855536186</v>
       </c>
       <c r="N2" t="n">
-        <v>8.309485501472373</v>
+        <v>8.29501808942825</v>
       </c>
       <c r="O2" t="n">
-        <v>2.882617820917711</v>
+        <v>2.880107305193376</v>
       </c>
       <c r="P2" t="n">
-        <v>215.6937202773805</v>
+        <v>215.6813596272743</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31742,28 +31835,28 @@
         <v>0.0954</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0496331393049659</v>
+        <v>-0.04896847448484577</v>
       </c>
       <c r="J3" t="n">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="K3" t="n">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01832288163142359</v>
+        <v>0.01796254120688623</v>
       </c>
       <c r="M3" t="n">
-        <v>2.268591927600975</v>
+        <v>2.264979304335056</v>
       </c>
       <c r="N3" t="n">
-        <v>7.805345242557572</v>
+        <v>7.784988089398655</v>
       </c>
       <c r="O3" t="n">
-        <v>2.793804796788346</v>
+        <v>2.790159151266941</v>
       </c>
       <c r="P3" t="n">
-        <v>210.5740204953906</v>
+        <v>210.5670883551987</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31814,28 +31907,28 @@
         <v>0.1109</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07281831054300403</v>
+        <v>-0.07414154164411188</v>
       </c>
       <c r="J4" t="n">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="K4" t="n">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04644751672124081</v>
+        <v>0.04829911306396018</v>
       </c>
       <c r="M4" t="n">
-        <v>2.002786053282105</v>
+        <v>2.003062091199176</v>
       </c>
       <c r="N4" t="n">
-        <v>6.437793374547754</v>
+        <v>6.432044930807797</v>
       </c>
       <c r="O4" t="n">
-        <v>2.537280704720657</v>
+        <v>2.536147655561047</v>
       </c>
       <c r="P4" t="n">
-        <v>203.2893534046953</v>
+        <v>203.3031560954819</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31873,7 +31966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E959"/>
+  <dimension ref="A1:E962"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57765,6 +57858,87 @@
         </is>
       </c>
     </row>
+    <row r="960">
+      <c r="A960" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:16+00:00</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>-41.019446025742695,173.01844384913335</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>-41.01874759206974,173.01847637478969</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>-41.018073809908614,173.01874457340745</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>-41.0194460139039,173.01844337363474</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>-41.0187475365758,173.01847602558072</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>-41.01807547858198,173.01874707068802</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>-41.01944588663679,173.018438262025</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>-41.01874616772507,173.01846741176024</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>-41.01807369071765,173.01874439503027</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
